--- a/campus-tests/SIT Master/Aptitude/set4_medium.xlsx
+++ b/campus-tests/SIT Master/Aptitude/set4_medium.xlsx
@@ -702,32 +702,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>easy</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Find the next number in the series: 5, 10, 15, ?</t>
+          <t>Find the next number in the series: 5, 9, 16, 26, 39, ?</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -752,27 +752,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Find the next number in the series: 7, 14, 28, ?</t>
+          <t>Find the next number in the series: 7, 14, 17, 34, 37, ?</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>68</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>71</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>74</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
     </row>
